--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF003F3-D4FB-4A7E-B97A-2D6A194A43FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A8066F-C28D-4425-A91C-6F3E1650760C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8910" yWindow="5210" windowWidth="26820" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8470" yWindow="4260" windowWidth="26820" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -748,11 +748,11 @@
         <v>LSE-012</v>
       </c>
       <c r="I2" s="22" t="str">
-        <f>LOWER(H2 &amp; "-" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C2 &amp; IF(D2&lt;&gt;"", "-" &amp; D2, "") &amp; "-" &amp; E2 &amp; "-" &amp; F2 &amp; "-" &amp; G2, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
-        <v>lse-012-55-e-hamilton-ave-campbell-ca-95008</v>
+        <f>UPPER(H2) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C2 &amp; IF(D2&lt;&gt;"", "-" &amp; D2, "") &amp; "-" &amp; E2 &amp; "-" &amp; F2 &amp; "-" &amp; G2, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
+        <v>LSE-012-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J2" s="25">
-        <v>46356</v>
+        <v>46329</v>
       </c>
       <c r="K2" s="15" t="s">
         <v>35</v>
@@ -791,11 +791,11 @@
         <v>JSE-786</v>
       </c>
       <c r="I3" s="24" t="str">
-        <f t="shared" ref="I3:I8" si="1">LOWER(H3 &amp; "-" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C3 &amp; IF(D3&lt;&gt;"", "-" &amp; D3, "") &amp; "-" &amp; E3 &amp; "-" &amp; F3 &amp; "-" &amp; G3, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
-        <v>jse-786-55-e-hamilton-ave-campbell-ca-95008</v>
+        <f t="shared" ref="I3:I8" si="1">UPPER(H3) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C3 &amp; IF(D3&lt;&gt;"", "-" &amp; D3, "") &amp; "-" &amp; E3 &amp; "-" &amp; F3 &amp; "-" &amp; G3, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
+        <v>JSE-786-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J3" s="26">
-        <v>46356</v>
+        <v>46329</v>
       </c>
       <c r="K3" s="16" t="s">
         <v>35</v>
@@ -835,10 +835,10 @@
       </c>
       <c r="I4" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>lse-012-55-e-hamilton-ave-campbell-ca-95008</v>
+        <v>LSE-012-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J4" s="27">
-        <v>46356</v>
+        <v>46329</v>
       </c>
       <c r="K4" s="17" t="s">
         <v>35</v>
@@ -878,10 +878,10 @@
       </c>
       <c r="I5" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>ewu-515-3271-silver-creek-vista-san-jose-ca-95138</v>
+        <v>EWU-515-3271-silver-creek-vista-san-jose-ca-95138</v>
       </c>
       <c r="J5" s="26">
-        <v>46356</v>
+        <v>46329</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>35</v>
@@ -921,10 +921,10 @@
       </c>
       <c r="I6" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>fzr-430-5045-crescent-park-manor-palo-alto-ca-94301</v>
+        <v>FZR-430-5045-crescent-park-manor-palo-alto-ca-94301</v>
       </c>
       <c r="J6" s="27">
-        <v>46356</v>
+        <v>46329</v>
       </c>
       <c r="K6" s="17" t="s">
         <v>35</v>
@@ -964,10 +964,10 @@
       </c>
       <c r="I7" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>gyu-509-3044-almaden-country-club-san-jose-ca-95120</v>
+        <v>GYU-509-3044-almaden-country-club-san-jose-ca-95120</v>
       </c>
       <c r="J7" s="26">
-        <v>46356</v>
+        <v>46329</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>35</v>
@@ -1007,10 +1007,10 @@
       </c>
       <c r="I8" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>hqu-548-14550-big-basin-way-saratoga-ca-95070</v>
+        <v>HQU-548-14550-big-basin-way-saratoga-ca-95070</v>
       </c>
       <c r="J8" s="27">
-        <v>46356</v>
+        <v>46329</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>35</v>

--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A8066F-C28D-4425-A91C-6F3E1650760C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E8AF95-31F7-4DCA-A682-3BE7EBF4D2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8470" yWindow="4260" windowWidth="26820" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
   <si>
     <t>address</t>
   </si>
@@ -123,6 +123,9 @@
     <t>123-45-676</t>
   </si>
   <si>
+    <t>Claim Your 1% Listing Fee</t>
+  </si>
+  <si>
     <t>offer-expire</t>
   </si>
   <si>
@@ -138,10 +141,10 @@
     <t>Exclusive 1% Offer Expires In</t>
   </si>
   <si>
-    <t>Claim Your 2% Listing Fee</t>
-  </si>
-  <si>
     <t>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1% listing commission.</t>
+  </si>
+  <si>
+    <t>123-45-675</t>
   </si>
 </sst>
 </file>
@@ -709,16 +712,16 @@
         <v>16</v>
       </c>
       <c r="J1" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" s="13"/>
     </row>
@@ -752,13 +755,13 @@
         <v>LSE-012-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J2" s="25">
-        <v>46329</v>
+        <v>46356</v>
       </c>
       <c r="K2" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>34</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>36</v>
@@ -795,13 +798,13 @@
         <v>JSE-786-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J3" s="26">
-        <v>46329</v>
+        <v>46356</v>
       </c>
       <c r="K3" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="16" t="s">
         <v>35</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>34</v>
       </c>
       <c r="M3" s="16" t="s">
         <v>36</v>
@@ -814,7 +817,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>18</v>
@@ -831,20 +834,20 @@
       </c>
       <c r="H4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>LSE-012</v>
+        <v>ISE-673</v>
       </c>
       <c r="I4" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>LSE-012-55-e-hamilton-ave-campbell-ca-95008</v>
+        <v>ISE-673-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J4" s="27">
-        <v>46329</v>
+        <v>46356</v>
       </c>
       <c r="K4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>34</v>
       </c>
       <c r="M4" s="17" t="s">
         <v>36</v>
@@ -881,13 +884,13 @@
         <v>EWU-515-3271-silver-creek-vista-san-jose-ca-95138</v>
       </c>
       <c r="J5" s="26">
-        <v>46329</v>
+        <v>46356</v>
       </c>
       <c r="K5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="16" t="s">
         <v>35</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>34</v>
       </c>
       <c r="M5" s="16" t="s">
         <v>36</v>
@@ -924,13 +927,13 @@
         <v>FZR-430-5045-crescent-park-manor-palo-alto-ca-94301</v>
       </c>
       <c r="J6" s="27">
-        <v>46329</v>
+        <v>46356</v>
       </c>
       <c r="K6" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>34</v>
       </c>
       <c r="M6" s="17" t="s">
         <v>36</v>
@@ -967,13 +970,13 @@
         <v>GYU-509-3044-almaden-country-club-san-jose-ca-95120</v>
       </c>
       <c r="J7" s="26">
-        <v>46329</v>
+        <v>46356</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>35</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>34</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>36</v>
@@ -1010,13 +1013,13 @@
         <v>HQU-548-14550-big-basin-way-saratoga-ca-95070</v>
       </c>
       <c r="J8" s="27">
-        <v>46329</v>
+        <v>46356</v>
       </c>
       <c r="K8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>34</v>
       </c>
       <c r="M8" s="17" t="s">
         <v>36</v>

--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E8AF95-31F7-4DCA-A682-3BE7EBF4D2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC190C67-6022-4EBF-BE91-63DFC5E17591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8470" yWindow="4260" windowWidth="26820" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
         <v>LSE-012-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J2" s="25">
-        <v>46356</v>
+        <v>46371</v>
       </c>
       <c r="K2" s="15" t="s">
         <v>30</v>
@@ -798,7 +798,7 @@
         <v>JSE-786-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J3" s="26">
-        <v>46356</v>
+        <v>46371</v>
       </c>
       <c r="K3" s="16" t="s">
         <v>30</v>
@@ -841,7 +841,7 @@
         <v>ISE-673-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
       <c r="J4" s="27">
-        <v>46356</v>
+        <v>46371</v>
       </c>
       <c r="K4" s="17" t="s">
         <v>30</v>
@@ -884,7 +884,7 @@
         <v>EWU-515-3271-silver-creek-vista-san-jose-ca-95138</v>
       </c>
       <c r="J5" s="26">
-        <v>46356</v>
+        <v>46371</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>30</v>
@@ -927,7 +927,7 @@
         <v>FZR-430-5045-crescent-park-manor-palo-alto-ca-94301</v>
       </c>
       <c r="J6" s="27">
-        <v>46356</v>
+        <v>46371</v>
       </c>
       <c r="K6" s="17" t="s">
         <v>30</v>
@@ -970,7 +970,7 @@
         <v>GYU-509-3044-almaden-country-club-san-jose-ca-95120</v>
       </c>
       <c r="J7" s="26">
-        <v>46356</v>
+        <v>46371</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>30</v>
@@ -1013,7 +1013,7 @@
         <v>HQU-548-14550-big-basin-way-saratoga-ca-95070</v>
       </c>
       <c r="J8" s="27">
-        <v>46356</v>
+        <v>46371</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>30</v>

--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC190C67-6022-4EBF-BE91-63DFC5E17591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF11D354-E402-4940-A97A-B392A12BBDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8470" yWindow="4260" windowWidth="26820" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12150" yWindow="3430" windowWidth="23290" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
   <si>
     <t>address</t>
   </si>
@@ -145,6 +145,30 @@
   </si>
   <si>
     <t>123-45-675</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Carol Pefley</t>
+  </si>
+  <si>
+    <t>Alex Yap</t>
+  </si>
+  <si>
+    <t>Michael Angeles</t>
+  </si>
+  <si>
+    <t>Tim Allen</t>
+  </si>
+  <si>
+    <t>John Smith</t>
+  </si>
+  <si>
+    <t>Kim So</t>
+  </si>
+  <si>
+    <t>Fatima Short</t>
   </si>
 </sst>
 </file>
@@ -152,7 +176,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -336,7 +360,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -354,13 +378,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -665,368 +689,392 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.6328125" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" customWidth="1"/>
-    <col min="3" max="3" width="19.26953125" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" customWidth="1"/>
-    <col min="6" max="6" width="5.1796875" customWidth="1"/>
-    <col min="7" max="7" width="6.08984375" customWidth="1"/>
-    <col min="8" max="9" width="24.7265625" customWidth="1"/>
-    <col min="10" max="10" width="16.453125" customWidth="1"/>
-    <col min="11" max="11" width="20.08984375" customWidth="1"/>
-    <col min="12" max="12" width="25.36328125" customWidth="1"/>
-    <col min="13" max="13" width="71.7265625" customWidth="1"/>
-    <col min="14" max="14" width="2.90625" customWidth="1"/>
+    <col min="2" max="3" width="13.1796875" customWidth="1"/>
+    <col min="4" max="4" width="19.26953125" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" customWidth="1"/>
+    <col min="8" max="8" width="6.08984375" customWidth="1"/>
+    <col min="9" max="10" width="24.7265625" customWidth="1"/>
+    <col min="11" max="11" width="16.453125" customWidth="1"/>
+    <col min="12" max="12" width="20.08984375" customWidth="1"/>
+    <col min="13" max="13" width="25.36328125" customWidth="1"/>
+    <col min="14" max="14" width="71.7265625" customWidth="1"/>
+    <col min="15" max="15" width="2.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="K1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
-        <f>MAX(A3:A983) + 1</f>
+        <f t="shared" ref="A2:A8" si="0">MAX(A3:A983) + 1</f>
         <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="15"/>
+      <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>95008</v>
       </c>
-      <c r="H2" s="21" t="str">
-        <f>UPPER(CHAR(65+MOD(CODE(LEFT(B2,1))+CODE(RIGHT(B2,1))+LEN(B2),26)) &amp; CHAR(65+MOD(CODE(LEFT(C2,1))+LEN(C2),26)) &amp; CHAR(65+MOD(CODE(LEFT(E2,1))+CODE(LEFT(F2,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B2,1))*113 + CODE(MID(B2,7,1))*73 + CODE(LEFT(C2,1))*37 + LEN(D2)*31 + CODE(LEFT(E2,1))*23 + CODE(LEFT(F2,1))*19 + CODE(RIGHT(G2,1))*29),1000),"000"))</f>
-        <v>LSE-012</v>
-      </c>
-      <c r="I2" s="22" t="str">
-        <f>UPPER(H2) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C2 &amp; IF(D2&lt;&gt;"", "-" &amp; D2, "") &amp; "-" &amp; E2 &amp; "-" &amp; F2 &amp; "-" &amp; G2, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
-        <v>LSE-012-55-e-hamilton-ave-campbell-ca-95008</v>
-      </c>
-      <c r="J2" s="25">
+      <c r="I2" s="21" t="str">
+        <f t="shared" ref="I2:I7" si="1">UPPER(CHAR(65+MOD(CODE(LEFT(B2,1))+CODE(LEFT(C2,1))+CODE(RIGHT(B2,1))+LEN(B2),26)) &amp; CHAR(65+MOD(CODE(LEFT(D2,1))+LEN(D2)+LEN(C2),26)) &amp; CHAR(65+MOD(CODE(LEFT(F2,1))+CODE(LEFT(G2,1))+CODE(LEFT(C2,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B2,1))*113 + CODE(MID(B2,7,1))*73 + CODE(LEFT(D2,1))*37 + CODE(LEFT(C2,1))*43 + LEN(E2)*31 + CODE(LEFT(F2,1))*23 + CODE(LEFT(G2,1))*19 + CODE(RIGHT(H2,1))*29),1000),"000"))</f>
+        <v>AET-893</v>
+      </c>
+      <c r="J2" s="22" t="str">
+        <f>UPPER(I2) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2 &amp; IF(E2&lt;&gt;"", "-" &amp; E2, "") &amp; "-" &amp; F2 &amp; "-" &amp; G2 &amp; "-" &amp; H2, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
+        <v>AET-893-55-e-hamilton-ave-campbell-ca-95008</v>
+      </c>
+      <c r="K2" s="25">
         <v>46371</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="M2" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
     </row>
-    <row r="3" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
-        <f>MAX(A4:A984) + 1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="7" t="str">
-        <f t="shared" ref="H3:H8" si="0">UPPER(CHAR(65+MOD(CODE(LEFT(B3,1))+CODE(RIGHT(B3,1))+LEN(B3),26)) &amp; CHAR(65+MOD(CODE(LEFT(C3,1))+LEN(C3),26)) &amp; CHAR(65+MOD(CODE(LEFT(E3,1))+CODE(LEFT(F3,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B3,1))*113 + CODE(MID(B3,7,1))*73 + CODE(LEFT(C3,1))*37 + LEN(D3)*31 + CODE(LEFT(E3,1))*23 + CODE(LEFT(F3,1))*19 + CODE(RIGHT(G3,1))*29),1000),"000"))</f>
-        <v>JSE-786</v>
-      </c>
-      <c r="I3" s="24" t="str">
-        <f t="shared" ref="I3:I8" si="1">UPPER(H3) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C3 &amp; IF(D3&lt;&gt;"", "-" &amp; D3, "") &amp; "-" &amp; E3 &amp; "-" &amp; F3 &amp; "-" &amp; G3, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
-        <v>JSE-786-55-e-hamilton-ave-campbell-ca-95008</v>
-      </c>
-      <c r="J3" s="26">
+      <c r="I3" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>WAR-581</v>
+      </c>
+      <c r="J3" s="24" t="str">
+        <f t="shared" ref="J3:J8" si="2">UPPER(I3) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D3 &amp; IF(E3&lt;&gt;"", "-" &amp; E3, "") &amp; "-" &amp; F3 &amp; "-" &amp; G3 &amp; "-" &amp; H3, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
+        <v>WAR-581-55-e-hamilton-ave-campbell-ca-95008</v>
+      </c>
+      <c r="K3" s="26">
         <v>46371</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="L3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="M3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="N3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
-    <row r="4" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
-        <f>MAX(A5:A985) + 1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="6" t="str">
+      <c r="I4" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>HHD-984</v>
+      </c>
+      <c r="J4" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>HHD-984-55-e-hamilton-ave-campbell-ca-95008</v>
+      </c>
+      <c r="K4" s="27">
+        <v>46371</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="13"/>
+    </row>
+    <row r="5" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
         <f t="shared" si="0"/>
-        <v>ISE-673</v>
-      </c>
-      <c r="I4" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>ISE-673-55-e-hamilton-ave-campbell-ca-95008</v>
-      </c>
-      <c r="J4" s="27">
-        <v>46371</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="13"/>
-    </row>
-    <row r="5" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
-        <f>MAX(A6:A986) + 1</f>
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="16"/>
+      <c r="F5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="I5" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>KFA-127</v>
+      </c>
+      <c r="J5" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>KFA-127-3271-silver-creek-vista-san-jose-ca-95138</v>
+      </c>
+      <c r="K5" s="26">
+        <v>46371</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="13"/>
+    </row>
+    <row r="6" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6">
         <f t="shared" si="0"/>
-        <v>EWU-515</v>
-      </c>
-      <c r="I5" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>EWU-515-3271-silver-creek-vista-san-jose-ca-95138</v>
-      </c>
-      <c r="J5" s="26">
-        <v>46371</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="13"/>
-    </row>
-    <row r="6" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
-        <f>MAX(A7:A987) + 1</f>
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="17"/>
+      <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="I6" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>BJN-612</v>
+      </c>
+      <c r="J6" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>BJN-612-5045-crescent-park-manor-palo-alto-ca-94301</v>
+      </c>
+      <c r="K6" s="27">
+        <v>46371</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="13"/>
+    </row>
+    <row r="7" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10">
         <f t="shared" si="0"/>
-        <v>FZR-430</v>
-      </c>
-      <c r="I6" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>FZR-430-5045-crescent-park-manor-palo-alto-ca-94301</v>
-      </c>
-      <c r="J6" s="27">
-        <v>46371</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" s="13"/>
-    </row>
-    <row r="7" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
-        <f>MAX(A8:A988) + 1</f>
         <v>2</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="16"/>
+      <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="I7" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>DER-734</v>
+      </c>
+      <c r="J7" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>DER-734-3044-almaden-country-club-san-jose-ca-95120</v>
+      </c>
+      <c r="K7" s="26">
+        <v>46371</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="13"/>
+    </row>
+    <row r="8" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
         <f t="shared" si="0"/>
-        <v>GYU-509</v>
-      </c>
-      <c r="I7" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>GYU-509-3044-almaden-country-club-san-jose-ca-95120</v>
-      </c>
-      <c r="J7" s="26">
-        <v>46371</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7" s="13"/>
-    </row>
-    <row r="8" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
-        <f>MAX(A9:A989) + 1</f>
         <v>1</v>
       </c>
       <c r="B8" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="17"/>
+      <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>HQU-548</v>
-      </c>
-      <c r="I8" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>HQU-548-14550-big-basin-way-saratoga-ca-95070</v>
-      </c>
-      <c r="J8" s="27">
+      <c r="I8" s="6" t="str">
+        <f>UPPER(CHAR(65+MOD(CODE(LEFT(B8,1))+CODE(LEFT(C8,1))+CODE(RIGHT(B8,1))+LEN(B8),26)) &amp; CHAR(65+MOD(CODE(LEFT(D8,1))+LEN(D8)+LEN(C8),26)) &amp; CHAR(65+MOD(CODE(LEFT(F8,1))+CODE(LEFT(G8,1))+CODE(LEFT(C8,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B8,1))*113 + CODE(MID(B8,7,1))*73 + CODE(LEFT(D8,1))*37 + CODE(LEFT(C8,1))*43 + LEN(E8)*31 + CODE(LEFT(F8,1))*23 + CODE(LEFT(G8,1))*19 + CODE(RIGHT(H8,1))*29),1000),"000"))</f>
+        <v>ZCM-558</v>
+      </c>
+      <c r="J8" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>ZCM-558-14550-big-basin-way-saratoga-ca-95070</v>
+      </c>
+      <c r="K8" s="27">
         <v>46371</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="L8" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="M8" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="N8" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1041,11 +1089,12 @@
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError sqref="G1:G8" numberStoredAsText="1"/>
+    <ignoredError sqref="H1:H8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF11D354-E402-4940-A97A-B392A12BBDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDBDA44-C5FE-4384-9BE1-BDD661595373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12150" yWindow="3430" windowWidth="23290" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
   <si>
     <t>address</t>
   </si>
@@ -123,9 +123,6 @@
     <t>123-45-676</t>
   </si>
   <si>
-    <t>Claim Your 1% Listing Fee</t>
-  </si>
-  <si>
     <t>offer-expire</t>
   </si>
   <si>
@@ -169,6 +166,9 @@
   </si>
   <si>
     <t>Fatima Short</t>
+  </si>
+  <si>
+    <t>commission</t>
   </si>
 </sst>
 </file>
@@ -178,7 +178,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +232,13 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -303,10 +310,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -387,9 +395,25 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -689,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.6328125" customWidth="1"/>
@@ -699,15 +723,16 @@
     <col min="6" max="6" width="12.1796875" customWidth="1"/>
     <col min="7" max="7" width="5.1796875" customWidth="1"/>
     <col min="8" max="8" width="6.08984375" customWidth="1"/>
-    <col min="9" max="10" width="24.7265625" customWidth="1"/>
-    <col min="11" max="11" width="16.453125" customWidth="1"/>
-    <col min="12" max="12" width="20.08984375" customWidth="1"/>
-    <col min="13" max="13" width="25.36328125" customWidth="1"/>
-    <col min="14" max="14" width="71.7265625" customWidth="1"/>
-    <col min="15" max="15" width="2.90625" customWidth="1"/>
+    <col min="9" max="9" width="13.26953125" customWidth="1"/>
+    <col min="10" max="11" width="24.7265625" customWidth="1"/>
+    <col min="12" max="12" width="16.453125" customWidth="1"/>
+    <col min="13" max="13" width="24.7265625" customWidth="1"/>
+    <col min="14" max="14" width="25.36328125" customWidth="1"/>
+    <col min="15" max="15" width="71.7265625" customWidth="1"/>
+    <col min="16" max="16" width="2.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>17</v>
       </c>
@@ -715,7 +740,7 @@
         <v>21</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>0</v>
@@ -732,27 +757,30 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="L1" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
-    <row r="2" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <f t="shared" ref="A2:A8" si="0">MAX(A3:A983) + 1</f>
         <v>7</v>
@@ -761,7 +789,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>18</v>
@@ -776,29 +804,33 @@
       <c r="H2" s="2">
         <v>95008</v>
       </c>
-      <c r="I2" s="21" t="str">
-        <f t="shared" ref="I2:I7" si="1">UPPER(CHAR(65+MOD(CODE(LEFT(B2,1))+CODE(LEFT(C2,1))+CODE(RIGHT(B2,1))+LEN(B2),26)) &amp; CHAR(65+MOD(CODE(LEFT(D2,1))+LEN(D2)+LEN(C2),26)) &amp; CHAR(65+MOD(CODE(LEFT(F2,1))+CODE(LEFT(G2,1))+CODE(LEFT(C2,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B2,1))*113 + CODE(MID(B2,7,1))*73 + CODE(LEFT(D2,1))*37 + CODE(LEFT(C2,1))*43 + LEN(E2)*31 + CODE(LEFT(F2,1))*23 + CODE(LEFT(G2,1))*19 + CODE(RIGHT(H2,1))*29),1000),"000"))</f>
+      <c r="I2" s="28">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="J2" s="21" t="str">
+        <f t="shared" ref="J2:J7" si="1">UPPER(CHAR(65+MOD(CODE(LEFT(B2,1))+CODE(LEFT(C2,1))+CODE(RIGHT(B2,1))+LEN(B2),26)) &amp; CHAR(65+MOD(CODE(LEFT(D2,1))+LEN(D2)+LEN(C2),26)) &amp; CHAR(65+MOD(CODE(LEFT(F2,1))+CODE(LEFT(G2,1))+CODE(LEFT(C2,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B2,1))*113 + CODE(MID(B2,7,1))*73 + CODE(LEFT(D2,1))*37 + CODE(LEFT(C2,1))*43 + LEN(E2)*31 + CODE(LEFT(F2,1))*23 + CODE(LEFT(G2,1))*19 + CODE(RIGHT(H2,1))*29),1000),"000"))</f>
         <v>AET-893</v>
       </c>
-      <c r="J2" s="22" t="str">
-        <f>UPPER(I2) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2 &amp; IF(E2&lt;&gt;"", "-" &amp; E2, "") &amp; "-" &amp; F2 &amp; "-" &amp; G2 &amp; "-" &amp; H2, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
+      <c r="K2" s="22" t="str">
+        <f>UPPER(J2) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2 &amp; IF(E2&lt;&gt;"", "-" &amp; E2, "") &amp; "-" &amp; F2 &amp; "-" &amp; G2 &amp; "-" &amp; H2, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
         <v>AET-893-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="K2" s="25">
+      <c r="L2" s="25">
         <v>46371</v>
       </c>
-      <c r="L2" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="30" t="str">
+        <f>"Claim Your "&amp;TEXT(I2, "0.##%")&amp;" Listing Fee"</f>
+        <v>Claim Your 1.25% Listing Fee</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
     </row>
-    <row r="3" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -807,7 +839,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>18</v>
@@ -822,38 +854,42 @@
       <c r="H3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="7" t="str">
+      <c r="I3" s="29">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J3" s="7" t="str">
         <f t="shared" si="1"/>
         <v>WAR-581</v>
       </c>
-      <c r="J3" s="24" t="str">
-        <f t="shared" ref="J3:J8" si="2">UPPER(I3) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D3 &amp; IF(E3&lt;&gt;"", "-" &amp; E3, "") &amp; "-" &amp; F3 &amp; "-" &amp; G3 &amp; "-" &amp; H3, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
+      <c r="K3" s="24" t="str">
+        <f t="shared" ref="K3:K8" si="2">UPPER(J3) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D3 &amp; IF(E3&lt;&gt;"", "-" &amp; E3, "") &amp; "-" &amp; F3 &amp; "-" &amp; G3 &amp; "-" &amp; H3, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
         <v>WAR-581-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="K3" s="26">
+      <c r="L3" s="26">
         <v>46371</v>
       </c>
-      <c r="L3" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="31" t="str">
+        <f t="shared" ref="M3:M8" si="3">"Claim Your "&amp;TEXT(I3, "0.##%")&amp;" Listing Fee"</f>
+        <v>Claim Your 2.5% Listing Fee</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
     </row>
-    <row r="4" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>18</v>
@@ -868,29 +904,33 @@
       <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="6" t="str">
+      <c r="I4" s="28">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J4" s="6" t="str">
         <f t="shared" si="1"/>
         <v>HHD-984</v>
       </c>
-      <c r="J4" s="11" t="str">
+      <c r="K4" s="11" t="str">
         <f t="shared" si="2"/>
         <v>HHD-984-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="K4" s="27">
+      <c r="L4" s="27">
         <v>46371</v>
       </c>
-      <c r="L4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Claim Your 2.5% Listing Fee</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N4" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
     </row>
-    <row r="5" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -899,7 +939,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>6</v>
@@ -914,29 +954,33 @@
       <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="29">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J5" s="7" t="str">
         <f t="shared" si="1"/>
         <v>KFA-127</v>
       </c>
-      <c r="J5" s="24" t="str">
+      <c r="K5" s="24" t="str">
         <f t="shared" si="2"/>
         <v>KFA-127-3271-silver-creek-vista-san-jose-ca-95138</v>
       </c>
-      <c r="K5" s="26">
+      <c r="L5" s="26">
         <v>46371</v>
       </c>
-      <c r="L5" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>Claim Your 2.5% Listing Fee</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
     </row>
-    <row r="6" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -945,7 +989,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>9</v>
@@ -960,29 +1004,33 @@
       <c r="H6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="28">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>BJN-612</v>
       </c>
-      <c r="J6" s="11" t="str">
+      <c r="K6" s="11" t="str">
         <f t="shared" si="2"/>
         <v>BJN-612-5045-crescent-park-manor-palo-alto-ca-94301</v>
       </c>
-      <c r="K6" s="27">
+      <c r="L6" s="27">
         <v>46371</v>
       </c>
-      <c r="L6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Claim Your 2.5% Listing Fee</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
     </row>
-    <row r="7" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -991,7 +1039,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>12</v>
@@ -1006,29 +1054,33 @@
       <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="29">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J7" s="7" t="str">
         <f t="shared" si="1"/>
         <v>DER-734</v>
       </c>
-      <c r="J7" s="24" t="str">
+      <c r="K7" s="24" t="str">
         <f t="shared" si="2"/>
         <v>DER-734-3044-almaden-country-club-san-jose-ca-95120</v>
       </c>
-      <c r="K7" s="26">
+      <c r="L7" s="26">
         <v>46371</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>Claim Your 2.5% Listing Fee</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="N7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
     </row>
-    <row r="8" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1037,7 +1089,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>14</v>
@@ -1052,29 +1104,33 @@
       <c r="H8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="6" t="str">
+      <c r="I8" s="28">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J8" s="6" t="str">
         <f>UPPER(CHAR(65+MOD(CODE(LEFT(B8,1))+CODE(LEFT(C8,1))+CODE(RIGHT(B8,1))+LEN(B8),26)) &amp; CHAR(65+MOD(CODE(LEFT(D8,1))+LEN(D8)+LEN(C8),26)) &amp; CHAR(65+MOD(CODE(LEFT(F8,1))+CODE(LEFT(G8,1))+CODE(LEFT(C8,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B8,1))*113 + CODE(MID(B8,7,1))*73 + CODE(LEFT(D8,1))*37 + CODE(LEFT(C8,1))*43 + LEN(E8)*31 + CODE(LEFT(F8,1))*23 + CODE(LEFT(G8,1))*19 + CODE(RIGHT(H8,1))*29),1000),"000"))</f>
         <v>ZCM-558</v>
       </c>
-      <c r="J8" s="11" t="str">
+      <c r="K8" s="11" t="str">
         <f t="shared" si="2"/>
         <v>ZCM-558-14550-big-basin-way-saratoga-ca-95070</v>
       </c>
-      <c r="K8" s="27">
+      <c r="L8" s="27">
         <v>46371</v>
       </c>
-      <c r="L8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Claim Your 2.5% Listing Fee</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1090,6 +1146,7 @@
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDBDA44-C5FE-4384-9BE1-BDD661595373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A07FB4-A39F-4282-88E6-1E658116D31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12150" yWindow="3430" windowWidth="23290" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <t>address</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>Exclusive 1% Offer Expires In</t>
-  </si>
-  <si>
-    <t>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1% listing commission.</t>
   </si>
   <si>
     <t>123-45-675</t>
@@ -740,7 +737,7 @@
         <v>21</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>0</v>
@@ -758,7 +755,7 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>27</v>
@@ -789,7 +786,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>18</v>
@@ -825,8 +822,9 @@
       <c r="N2" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="15" t="s">
-        <v>35</v>
+      <c r="O2" s="30" t="str">
+        <f>"Secure full representation, professional staging advisory, and maximum market exposure at an exclusive "&amp;TEXT(I2, "0.##%")&amp;" listing commission."</f>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
       <c r="P2" s="13"/>
     </row>
@@ -839,7 +837,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>18</v>
@@ -875,8 +873,9 @@
       <c r="N3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="16" t="s">
-        <v>35</v>
+      <c r="O3" s="16" t="str">
+        <f t="shared" ref="O3:O8" si="4">"Secure full representation, professional staging advisory, and maximum market exposure at an exclusive "&amp;TEXT(I3, "0.##%")&amp;" listing commission."</f>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
       </c>
       <c r="P3" s="13"/>
     </row>
@@ -886,10 +885,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>18</v>
@@ -925,8 +924,9 @@
       <c r="N4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="17" t="s">
-        <v>35</v>
+      <c r="O4" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
       </c>
       <c r="P4" s="13"/>
     </row>
@@ -939,7 +939,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>6</v>
@@ -975,8 +975,9 @@
       <c r="N5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="O5" s="16" t="s">
-        <v>35</v>
+      <c r="O5" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
       </c>
       <c r="P5" s="13"/>
     </row>
@@ -989,7 +990,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>9</v>
@@ -1025,8 +1026,9 @@
       <c r="N6" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="17" t="s">
-        <v>35</v>
+      <c r="O6" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
       </c>
       <c r="P6" s="13"/>
     </row>
@@ -1039,7 +1041,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>12</v>
@@ -1075,8 +1077,9 @@
       <c r="N7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="O7" s="16" t="s">
-        <v>35</v>
+      <c r="O7" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
       </c>
       <c r="P7" s="13"/>
     </row>
@@ -1089,7 +1092,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>14</v>
@@ -1125,8 +1128,9 @@
       <c r="N8" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="O8" s="17" t="s">
-        <v>35</v>
+      <c r="O8" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
       </c>
       <c r="P8" s="13"/>
     </row>

--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A07FB4-A39F-4282-88E6-1E658116D31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ADD938-A07C-4199-A803-2E76E05A2851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12150" yWindow="3430" windowWidth="23290" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>address</t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>offer-headline-3</t>
-  </si>
-  <si>
-    <t>Exclusive 1% Offer Expires In</t>
   </si>
   <si>
     <t>123-45-675</t>
@@ -737,7 +734,7 @@
         <v>21</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>0</v>
@@ -755,7 +752,7 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>27</v>
@@ -786,7 +783,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>18</v>
@@ -819,8 +816,9 @@
         <f>"Claim Your "&amp;TEXT(I2, "0.##%")&amp;" Listing Fee"</f>
         <v>Claim Your 1.25% Listing Fee</v>
       </c>
-      <c r="N2" s="17" t="s">
-        <v>34</v>
+      <c r="N2" s="32" t="str">
+        <f>"Exclusive "&amp;TEXT(I2, "0.##%")&amp;" Offer Expires In"</f>
+        <v>Exclusive 1.25% Offer Expires In</v>
       </c>
       <c r="O2" s="30" t="str">
         <f>"Secure full representation, professional staging advisory, and maximum market exposure at an exclusive "&amp;TEXT(I2, "0.##%")&amp;" listing commission."</f>
@@ -837,7 +835,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>18</v>
@@ -853,7 +851,7 @@
         <v>20</v>
       </c>
       <c r="I3" s="29">
-        <v>2.5000000000000001E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J3" s="7" t="str">
         <f t="shared" si="1"/>
@@ -868,14 +866,15 @@
       </c>
       <c r="M3" s="31" t="str">
         <f t="shared" ref="M3:M8" si="3">"Claim Your "&amp;TEXT(I3, "0.##%")&amp;" Listing Fee"</f>
-        <v>Claim Your 2.5% Listing Fee</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>34</v>
+        <v>Claim Your 1.25% Listing Fee</v>
+      </c>
+      <c r="N3" s="31" t="str">
+        <f t="shared" ref="N3:N8" si="4">"Exclusive "&amp;TEXT(I3, "0.##%")&amp;" Offer Expires In"</f>
+        <v>Exclusive 1.25% Offer Expires In</v>
       </c>
       <c r="O3" s="16" t="str">
-        <f t="shared" ref="O3:O8" si="4">"Secure full representation, professional staging advisory, and maximum market exposure at an exclusive "&amp;TEXT(I3, "0.##%")&amp;" listing commission."</f>
-        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
+        <f t="shared" ref="O3:O8" si="5">"Secure full representation, professional staging advisory, and maximum market exposure at an exclusive "&amp;TEXT(I3, "0.##%")&amp;" listing commission."</f>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
       <c r="P3" s="13"/>
     </row>
@@ -885,10 +884,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>18</v>
@@ -904,7 +903,7 @@
         <v>20</v>
       </c>
       <c r="I4" s="28">
-        <v>2.5000000000000001E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J4" s="6" t="str">
         <f t="shared" si="1"/>
@@ -919,14 +918,15 @@
       </c>
       <c r="M4" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 2.5% Listing Fee</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>34</v>
+        <v>Claim Your 1.25% Listing Fee</v>
+      </c>
+      <c r="N4" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>Exclusive 1.25% Offer Expires In</v>
       </c>
       <c r="O4" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
+        <f t="shared" si="5"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
       <c r="P4" s="13"/>
     </row>
@@ -939,7 +939,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>6</v>
@@ -955,7 +955,7 @@
         <v>8</v>
       </c>
       <c r="I5" s="29">
-        <v>2.5000000000000001E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J5" s="7" t="str">
         <f t="shared" si="1"/>
@@ -970,14 +970,15 @@
       </c>
       <c r="M5" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 2.5% Listing Fee</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>34</v>
+        <v>Claim Your 1.25% Listing Fee</v>
+      </c>
+      <c r="N5" s="31" t="str">
+        <f t="shared" si="4"/>
+        <v>Exclusive 1.25% Offer Expires In</v>
       </c>
       <c r="O5" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
+        <f t="shared" si="5"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
       <c r="P5" s="13"/>
     </row>
@@ -990,7 +991,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>9</v>
@@ -1006,7 +1007,7 @@
         <v>11</v>
       </c>
       <c r="I6" s="28">
-        <v>2.5000000000000001E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J6" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1021,14 +1022,15 @@
       </c>
       <c r="M6" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 2.5% Listing Fee</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>34</v>
+        <v>Claim Your 1.25% Listing Fee</v>
+      </c>
+      <c r="N6" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>Exclusive 1.25% Offer Expires In</v>
       </c>
       <c r="O6" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
+        <f t="shared" si="5"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
       <c r="P6" s="13"/>
     </row>
@@ -1041,7 +1043,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>12</v>
@@ -1057,7 +1059,7 @@
         <v>13</v>
       </c>
       <c r="I7" s="29">
-        <v>2.5000000000000001E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J7" s="7" t="str">
         <f t="shared" si="1"/>
@@ -1072,14 +1074,15 @@
       </c>
       <c r="M7" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 2.5% Listing Fee</v>
-      </c>
-      <c r="N7" s="16" t="s">
-        <v>34</v>
+        <v>Claim Your 1.25% Listing Fee</v>
+      </c>
+      <c r="N7" s="31" t="str">
+        <f t="shared" si="4"/>
+        <v>Exclusive 1.25% Offer Expires In</v>
       </c>
       <c r="O7" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
+        <f t="shared" si="5"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
       <c r="P7" s="13"/>
     </row>
@@ -1092,7 +1095,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>14</v>
@@ -1108,7 +1111,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="28">
-        <v>2.5000000000000001E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J8" s="6" t="str">
         <f>UPPER(CHAR(65+MOD(CODE(LEFT(B8,1))+CODE(LEFT(C8,1))+CODE(RIGHT(B8,1))+LEN(B8),26)) &amp; CHAR(65+MOD(CODE(LEFT(D8,1))+LEN(D8)+LEN(C8),26)) &amp; CHAR(65+MOD(CODE(LEFT(F8,1))+CODE(LEFT(G8,1))+CODE(LEFT(C8,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B8,1))*113 + CODE(MID(B8,7,1))*73 + CODE(LEFT(D8,1))*37 + CODE(LEFT(C8,1))*43 + LEN(E8)*31 + CODE(LEFT(F8,1))*23 + CODE(LEFT(G8,1))*19 + CODE(RIGHT(H8,1))*29),1000),"000"))</f>
@@ -1123,14 +1126,15 @@
       </c>
       <c r="M8" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 2.5% Listing Fee</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>34</v>
+        <v>Claim Your 1.25% Listing Fee</v>
+      </c>
+      <c r="N8" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>Exclusive 1.25% Offer Expires In</v>
       </c>
       <c r="O8" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 2.5% listing commission.</v>
+        <f t="shared" si="5"/>
+        <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
       <c r="P8" s="13"/>
     </row>

--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ADD938-A07C-4199-A803-2E76E05A2851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09ED73B-9472-4B3F-83C9-2D24A2761BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12150" yWindow="3430" windowWidth="23290" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8490" yWindow="2800" windowWidth="23290" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -172,7 +172,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +233,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -308,7 +313,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -380,15 +385,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -403,6 +399,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -763,10 +771,10 @@
       <c r="L1" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="33" t="s">
         <v>32</v>
       </c>
       <c r="O1" s="8" t="s">
@@ -798,7 +806,7 @@
       <c r="H2" s="2">
         <v>95008</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="25">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J2" s="21" t="str">
@@ -809,18 +817,18 @@
         <f>UPPER(J2) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2 &amp; IF(E2&lt;&gt;"", "-" &amp; E2, "") &amp; "-" &amp; F2 &amp; "-" &amp; G2 &amp; "-" &amp; H2, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
         <v>AET-893-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="L2" s="25">
+      <c r="L2" s="30">
         <v>46371</v>
       </c>
-      <c r="M2" s="30" t="str">
-        <f>"Claim Your "&amp;TEXT(I2, "0.##%")&amp;" Listing Fee"</f>
-        <v>Claim Your 1.25% Listing Fee</v>
-      </c>
-      <c r="N2" s="32" t="str">
+      <c r="M2" s="27" t="str">
+        <f>"Claim Your "&amp;TEXT(I2, "0.##%")&amp;" Listing Fee Today"</f>
+        <v>Claim Your 1.25% Listing Fee Today</v>
+      </c>
+      <c r="N2" s="29" t="str">
         <f>"Exclusive "&amp;TEXT(I2, "0.##%")&amp;" Offer Expires In"</f>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
-      <c r="O2" s="30" t="str">
+      <c r="O2" s="27" t="str">
         <f>"Secure full representation, professional staging advisory, and maximum market exposure at an exclusive "&amp;TEXT(I2, "0.##%")&amp;" listing commission."</f>
         <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
@@ -850,7 +858,7 @@
       <c r="H3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="26">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J3" s="7" t="str">
@@ -861,14 +869,14 @@
         <f t="shared" ref="K3:K8" si="2">UPPER(J3) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D3 &amp; IF(E3&lt;&gt;"", "-" &amp; E3, "") &amp; "-" &amp; F3 &amp; "-" &amp; G3 &amp; "-" &amp; H3, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
         <v>WAR-581-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="31">
         <v>46371</v>
       </c>
-      <c r="M3" s="31" t="str">
-        <f t="shared" ref="M3:M8" si="3">"Claim Your "&amp;TEXT(I3, "0.##%")&amp;" Listing Fee"</f>
-        <v>Claim Your 1.25% Listing Fee</v>
-      </c>
-      <c r="N3" s="31" t="str">
+      <c r="M3" s="28" t="str">
+        <f t="shared" ref="M3:M8" si="3">"Claim Your "&amp;TEXT(I3, "0.##%")&amp;" Listing Fee Today"</f>
+        <v>Claim Your 1.25% Listing Fee Today</v>
+      </c>
+      <c r="N3" s="28" t="str">
         <f t="shared" ref="N3:N8" si="4">"Exclusive "&amp;TEXT(I3, "0.##%")&amp;" Offer Expires In"</f>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
@@ -902,7 +910,7 @@
       <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="25">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J4" s="6" t="str">
@@ -913,14 +921,14 @@
         <f t="shared" si="2"/>
         <v>HHD-984-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="32">
         <v>46371</v>
       </c>
-      <c r="M4" s="32" t="str">
+      <c r="M4" s="29" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee</v>
-      </c>
-      <c r="N4" s="32" t="str">
+        <v>Claim Your 1.25% Listing Fee Today</v>
+      </c>
+      <c r="N4" s="29" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
@@ -954,7 +962,7 @@
       <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="26">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J5" s="7" t="str">
@@ -965,14 +973,14 @@
         <f t="shared" si="2"/>
         <v>KFA-127-3271-silver-creek-vista-san-jose-ca-95138</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="31">
         <v>46371</v>
       </c>
-      <c r="M5" s="31" t="str">
+      <c r="M5" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee</v>
-      </c>
-      <c r="N5" s="31" t="str">
+        <v>Claim Your 1.25% Listing Fee Today</v>
+      </c>
+      <c r="N5" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
@@ -1006,7 +1014,7 @@
       <c r="H6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="25">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J6" s="6" t="str">
@@ -1017,14 +1025,14 @@
         <f t="shared" si="2"/>
         <v>BJN-612-5045-crescent-park-manor-palo-alto-ca-94301</v>
       </c>
-      <c r="L6" s="27">
+      <c r="L6" s="32">
         <v>46371</v>
       </c>
-      <c r="M6" s="32" t="str">
+      <c r="M6" s="29" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee</v>
-      </c>
-      <c r="N6" s="32" t="str">
+        <v>Claim Your 1.25% Listing Fee Today</v>
+      </c>
+      <c r="N6" s="29" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
@@ -1058,7 +1066,7 @@
       <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="26">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J7" s="7" t="str">
@@ -1069,14 +1077,14 @@
         <f t="shared" si="2"/>
         <v>DER-734-3044-almaden-country-club-san-jose-ca-95120</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="31">
         <v>46371</v>
       </c>
-      <c r="M7" s="31" t="str">
+      <c r="M7" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee</v>
-      </c>
-      <c r="N7" s="31" t="str">
+        <v>Claim Your 1.25% Listing Fee Today</v>
+      </c>
+      <c r="N7" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
@@ -1110,7 +1118,7 @@
       <c r="H8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="25">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J8" s="6" t="str">
@@ -1121,14 +1129,14 @@
         <f t="shared" si="2"/>
         <v>ZCM-558-14550-big-basin-way-saratoga-ca-95070</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="32">
         <v>46371</v>
       </c>
-      <c r="M8" s="32" t="str">
+      <c r="M8" s="29" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee</v>
-      </c>
-      <c r="N8" s="32" t="str">
+        <v>Claim Your 1.25% Listing Fee Today</v>
+      </c>
+      <c r="N8" s="29" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>

--- a/src/data/offer.xlsx
+++ b/src/data/offer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09ED73B-9472-4B3F-83C9-2D24A2761BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14EAB50-04A6-4DED-B612-6C6A17AA573C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8490" yWindow="2800" windowWidth="23290" windowHeight="15890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8490" yWindow="2800" windowWidth="27600" windowHeight="16590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>address</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>commission</t>
+  </si>
+  <si>
+    <t>submit-button</t>
   </si>
 </sst>
 </file>
@@ -313,7 +316,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -336,9 +339,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -411,6 +411,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -715,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.6328125" customWidth="1"/>
@@ -731,26 +740,27 @@
     <col min="13" max="13" width="24.7265625" customWidth="1"/>
     <col min="14" max="14" width="25.36328125" customWidth="1"/>
     <col min="15" max="15" width="71.7265625" customWidth="1"/>
-    <col min="16" max="16" width="2.90625" customWidth="1"/>
+    <col min="16" max="16" width="39.1796875" customWidth="1"/>
+    <col min="17" max="17" width="2.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -762,27 +772,30 @@
       <c r="I1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="13"/>
+      <c r="P1" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <f t="shared" ref="A2:A8" si="0">MAX(A3:A983) + 1</f>
         <v>7</v>
@@ -793,10 +806,10 @@
       <c r="C2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="15"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
@@ -806,101 +819,109 @@
       <c r="H2" s="2">
         <v>95008</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="24">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="J2" s="21" t="str">
+      <c r="J2" s="20" t="str">
         <f t="shared" ref="J2:J7" si="1">UPPER(CHAR(65+MOD(CODE(LEFT(B2,1))+CODE(LEFT(C2,1))+CODE(RIGHT(B2,1))+LEN(B2),26)) &amp; CHAR(65+MOD(CODE(LEFT(D2,1))+LEN(D2)+LEN(C2),26)) &amp; CHAR(65+MOD(CODE(LEFT(F2,1))+CODE(LEFT(G2,1))+CODE(LEFT(C2,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B2,1))*113 + CODE(MID(B2,7,1))*73 + CODE(LEFT(D2,1))*37 + CODE(LEFT(C2,1))*43 + LEN(E2)*31 + CODE(LEFT(F2,1))*23 + CODE(LEFT(G2,1))*19 + CODE(RIGHT(H2,1))*29),1000),"000"))</f>
         <v>AET-893</v>
       </c>
-      <c r="K2" s="22" t="str">
+      <c r="K2" s="21" t="str">
         <f>UPPER(J2) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2 &amp; IF(E2&lt;&gt;"", "-" &amp; E2, "") &amp; "-" &amp; F2 &amp; "-" &amp; G2 &amp; "-" &amp; H2, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
         <v>AET-893-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="L2" s="30">
+      <c r="L2" s="29">
         <v>46371</v>
       </c>
-      <c r="M2" s="27" t="str">
-        <f>"Claim Your "&amp;TEXT(I2, "0.##%")&amp;" Listing Fee Today"</f>
-        <v>Claim Your 1.25% Listing Fee Today</v>
-      </c>
-      <c r="N2" s="29" t="str">
+      <c r="M2" s="26" t="str">
+        <f>"Lock in "&amp;TEXT(I2, "0.##%")&amp;" Listing Fee Now"</f>
+        <v>Lock in 1.25% Listing Fee Now</v>
+      </c>
+      <c r="N2" s="28" t="str">
         <f>"Exclusive "&amp;TEXT(I2, "0.##%")&amp;" Offer Expires In"</f>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
-      <c r="O2" s="27" t="str">
+      <c r="O2" s="26" t="str">
         <f>"Secure full representation, professional staging advisory, and maximum market exposure at an exclusive "&amp;TEXT(I2, "0.##%")&amp;" listing commission."</f>
         <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
-      <c r="P2" s="13"/>
+      <c r="P2" s="33" t="str">
+        <f>"Lock in Your "&amp;TEXT(I2, "0.##%")&amp;" Listing Fee"</f>
+        <v>Lock in Your 1.25% Listing Fee</v>
+      </c>
+      <c r="Q2" s="12"/>
     </row>
-    <row r="3" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10">
+    <row r="3" spans="1:17" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="16"/>
+      <c r="E3" s="15"/>
       <c r="F3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="25">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J3" s="7" t="str">
         <f t="shared" si="1"/>
         <v>WAR-581</v>
       </c>
-      <c r="K3" s="24" t="str">
+      <c r="K3" s="23" t="str">
         <f t="shared" ref="K3:K8" si="2">UPPER(J3) &amp; "-" &amp; LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D3 &amp; IF(E3&lt;&gt;"", "-" &amp; E3, "") &amp; "-" &amp; F3 &amp; "-" &amp; G3 &amp; "-" &amp; H3, "%", ""), ",", ""), ".", ""), "#", ""), "'", ""), "/", ""), " ", "-"))</f>
         <v>WAR-581-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="30">
         <v>46371</v>
       </c>
-      <c r="M3" s="28" t="str">
-        <f t="shared" ref="M3:M8" si="3">"Claim Your "&amp;TEXT(I3, "0.##%")&amp;" Listing Fee Today"</f>
-        <v>Claim Your 1.25% Listing Fee Today</v>
-      </c>
-      <c r="N3" s="28" t="str">
+      <c r="M3" s="27" t="str">
+        <f t="shared" ref="M3:M8" si="3">"Lock in "&amp;TEXT(I3, "0.##%")&amp;" Listing Fee Now"</f>
+        <v>Lock in 1.25% Listing Fee Now</v>
+      </c>
+      <c r="N3" s="27" t="str">
         <f t="shared" ref="N3:N8" si="4">"Exclusive "&amp;TEXT(I3, "0.##%")&amp;" Offer Expires In"</f>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
-      <c r="O3" s="16" t="str">
+      <c r="O3" s="27" t="str">
         <f t="shared" ref="O3:O8" si="5">"Secure full representation, professional staging advisory, and maximum market exposure at an exclusive "&amp;TEXT(I3, "0.##%")&amp;" listing commission."</f>
         <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
-      <c r="P3" s="13"/>
+      <c r="P3" s="34" t="str">
+        <f t="shared" ref="P3:P8" si="6">"Lock in Your "&amp;TEXT(I3, "0.##%")&amp;" Listing Fee"</f>
+        <v>Lock in Your 1.25% Listing Fee</v>
+      </c>
+      <c r="Q3" s="12"/>
     </row>
-    <row r="4" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="17"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
@@ -910,49 +931,53 @@
       <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="24">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J4" s="6" t="str">
         <f t="shared" si="1"/>
         <v>HHD-984</v>
       </c>
-      <c r="K4" s="11" t="str">
+      <c r="K4" s="10" t="str">
         <f t="shared" si="2"/>
         <v>HHD-984-55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="31">
         <v>46371</v>
       </c>
-      <c r="M4" s="29" t="str">
+      <c r="M4" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee Today</v>
-      </c>
-      <c r="N4" s="29" t="str">
+        <v>Lock in 1.25% Listing Fee Now</v>
+      </c>
+      <c r="N4" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
-      <c r="O4" s="17" t="str">
+      <c r="O4" s="28" t="str">
         <f t="shared" si="5"/>
         <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
-      <c r="P4" s="13"/>
+      <c r="P4" s="35" t="str">
+        <f t="shared" si="6"/>
+        <v>Lock in Your 1.25% Listing Fee</v>
+      </c>
+      <c r="Q4" s="12"/>
     </row>
-    <row r="5" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
+    <row r="5" spans="1:17" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="15"/>
       <c r="F5" s="5" t="s">
         <v>7</v>
       </c>
@@ -962,49 +987,53 @@
       <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="25">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J5" s="7" t="str">
         <f t="shared" si="1"/>
         <v>KFA-127</v>
       </c>
-      <c r="K5" s="24" t="str">
+      <c r="K5" s="23" t="str">
         <f t="shared" si="2"/>
         <v>KFA-127-3271-silver-creek-vista-san-jose-ca-95138</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="30">
         <v>46371</v>
       </c>
-      <c r="M5" s="28" t="str">
+      <c r="M5" s="27" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee Today</v>
-      </c>
-      <c r="N5" s="28" t="str">
+        <v>Lock in 1.25% Listing Fee Now</v>
+      </c>
+      <c r="N5" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
-      <c r="O5" s="16" t="str">
+      <c r="O5" s="27" t="str">
         <f t="shared" si="5"/>
         <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
-      <c r="P5" s="13"/>
+      <c r="P5" s="34" t="str">
+        <f t="shared" si="6"/>
+        <v>Lock in Your 1.25% Listing Fee</v>
+      </c>
+      <c r="Q5" s="12"/>
     </row>
-    <row r="6" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="17"/>
+      <c r="E6" s="16"/>
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
@@ -1014,49 +1043,53 @@
       <c r="H6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>BJN-612</v>
       </c>
-      <c r="K6" s="11" t="str">
+      <c r="K6" s="10" t="str">
         <f t="shared" si="2"/>
         <v>BJN-612-5045-crescent-park-manor-palo-alto-ca-94301</v>
       </c>
-      <c r="L6" s="32">
+      <c r="L6" s="31">
         <v>46371</v>
       </c>
-      <c r="M6" s="29" t="str">
+      <c r="M6" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee Today</v>
-      </c>
-      <c r="N6" s="29" t="str">
+        <v>Lock in 1.25% Listing Fee Now</v>
+      </c>
+      <c r="N6" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
-      <c r="O6" s="17" t="str">
+      <c r="O6" s="28" t="str">
         <f t="shared" si="5"/>
         <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="35" t="str">
+        <f t="shared" si="6"/>
+        <v>Lock in Your 1.25% Listing Fee</v>
+      </c>
+      <c r="Q6" s="12"/>
     </row>
-    <row r="7" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
+    <row r="7" spans="1:17" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1066,49 +1099,53 @@
       <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="25">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J7" s="7" t="str">
         <f t="shared" si="1"/>
         <v>DER-734</v>
       </c>
-      <c r="K7" s="24" t="str">
+      <c r="K7" s="23" t="str">
         <f t="shared" si="2"/>
         <v>DER-734-3044-almaden-country-club-san-jose-ca-95120</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="30">
         <v>46371</v>
       </c>
-      <c r="M7" s="28" t="str">
+      <c r="M7" s="27" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee Today</v>
-      </c>
-      <c r="N7" s="28" t="str">
+        <v>Lock in 1.25% Listing Fee Now</v>
+      </c>
+      <c r="N7" s="27" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
-      <c r="O7" s="16" t="str">
+      <c r="O7" s="27" t="str">
         <f t="shared" si="5"/>
         <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
-      <c r="P7" s="13"/>
+      <c r="P7" s="34" t="str">
+        <f t="shared" si="6"/>
+        <v>Lock in Your 1.25% Listing Fee</v>
+      </c>
+      <c r="Q7" s="12"/>
     </row>
-    <row r="8" spans="1:16" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="17"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
@@ -1118,51 +1155,56 @@
       <c r="H8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="24">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="J8" s="6" t="str">
         <f>UPPER(CHAR(65+MOD(CODE(LEFT(B8,1))+CODE(LEFT(C8,1))+CODE(RIGHT(B8,1))+LEN(B8),26)) &amp; CHAR(65+MOD(CODE(LEFT(D8,1))+LEN(D8)+LEN(C8),26)) &amp; CHAR(65+MOD(CODE(LEFT(F8,1))+CODE(LEFT(G8,1))+CODE(LEFT(C8,1)),26)) &amp; "-" &amp; TEXT(MOD(ABS(CODE(RIGHT(B8,1))*113 + CODE(MID(B8,7,1))*73 + CODE(LEFT(D8,1))*37 + CODE(LEFT(C8,1))*43 + LEN(E8)*31 + CODE(LEFT(F8,1))*23 + CODE(LEFT(G8,1))*19 + CODE(RIGHT(H8,1))*29),1000),"000"))</f>
         <v>ZCM-558</v>
       </c>
-      <c r="K8" s="11" t="str">
+      <c r="K8" s="10" t="str">
         <f t="shared" si="2"/>
         <v>ZCM-558-14550-big-basin-way-saratoga-ca-95070</v>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="31">
         <v>46371</v>
       </c>
-      <c r="M8" s="29" t="str">
+      <c r="M8" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>Claim Your 1.25% Listing Fee Today</v>
-      </c>
-      <c r="N8" s="29" t="str">
+        <v>Lock in 1.25% Listing Fee Now</v>
+      </c>
+      <c r="N8" s="28" t="str">
         <f t="shared" si="4"/>
         <v>Exclusive 1.25% Offer Expires In</v>
       </c>
-      <c r="O8" s="17" t="str">
+      <c r="O8" s="28" t="str">
         <f t="shared" si="5"/>
         <v>Secure full representation, professional staging advisory, and maximum market exposure at an exclusive 1.25% listing commission.</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="35" t="str">
+        <f t="shared" si="6"/>
+        <v>Lock in Your 1.25% Listing Fee</v>
+      </c>
+      <c r="Q8" s="12"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
